--- a/artfynd/A 28794-2023 artfynd.xlsx
+++ b/artfynd/A 28794-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116081862</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>116081861</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 28794-2023 artfynd.xlsx
+++ b/artfynd/A 28794-2023 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -803,11 +798,6 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 28794-2023 artfynd.xlsx
+++ b/artfynd/A 28794-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116081862</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -784,7 +789,7 @@
         <v>116081861</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,6 +803,11 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 28794-2023 artfynd.xlsx
+++ b/artfynd/A 28794-2023 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116081862</v>
+        <v>116081861</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558925</v>
+        <v>558744</v>
       </c>
       <c r="R2" t="n">
-        <v>6642225</v>
+        <v>6642080</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,19 +781,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116081861</v>
+        <v>116081862</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -835,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558744</v>
+        <v>558925</v>
       </c>
       <c r="R3" t="n">
-        <v>6642080</v>
+        <v>6642225</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
